--- a/Excel/OccupationJueXingConfig.xlsx
+++ b/Excel/OccupationJueXingConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566E3840-9C7B-4B9E-9F28-AB1422FC476F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6051133A-0965-405A-8AFA-5E3F6BB6FC18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OccupationJueXingProto" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="46">
   <si>
     <t>int</t>
     <phoneticPr fontId="23" type="noConversion"/>
@@ -174,6 +174,18 @@
   </si>
   <si>
     <t>69054031,69054032,69054033,69054034</t>
+  </si>
+  <si>
+    <t>69055001,69055002,69055003</t>
+  </si>
+  <si>
+    <t>69055011,69055012,69055013,69055014</t>
+  </si>
+  <si>
+    <t>69055021,69055022,69055023,69055024</t>
+  </si>
+  <si>
+    <t>69055031,69055032,69055033,69055034</t>
   </si>
 </sst>
 </file>
@@ -2556,7 +2568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:I77"/>
+  <dimension ref="C1:I95"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="14.125" customWidth="1"/>
@@ -3881,6 +3893,321 @@
         <v>29</v>
       </c>
     </row>
+    <row r="78" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C78" s="7">
+        <v>69055001</v>
+      </c>
+      <c r="D78" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E78" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I78" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="79" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C79" s="7">
+        <v>69055002</v>
+      </c>
+      <c r="D79" s="4">
+        <v>1500</v>
+      </c>
+      <c r="E79" s="4">
+        <v>1500000</v>
+      </c>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="80" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C80" s="7">
+        <v>69055003</v>
+      </c>
+      <c r="D80" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E80" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C81" s="7">
+        <v>69055011</v>
+      </c>
+      <c r="D81" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E81" s="4">
+        <v>3000000</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I81" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="82" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C82" s="7">
+        <v>69055012</v>
+      </c>
+      <c r="D82" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E82" s="4">
+        <v>3000000</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="83" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C83" s="7">
+        <v>69055013</v>
+      </c>
+      <c r="D83" s="4">
+        <v>4000</v>
+      </c>
+      <c r="E83" s="4">
+        <v>3000000</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="84" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C84" s="7">
+        <v>69055014</v>
+      </c>
+      <c r="D84" s="4">
+        <v>4000</v>
+      </c>
+      <c r="E84" s="4">
+        <v>3000000</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="85" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C85" s="7">
+        <v>69055021</v>
+      </c>
+      <c r="D85" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E85" s="4">
+        <v>3000000</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I85" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="86" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C86" s="7">
+        <v>69055022</v>
+      </c>
+      <c r="D86" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E86" s="4">
+        <v>3000000</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="87" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C87" s="7">
+        <v>69055023</v>
+      </c>
+      <c r="D87" s="4">
+        <v>4000</v>
+      </c>
+      <c r="E87" s="4">
+        <v>3000000</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="88" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C88" s="7">
+        <v>69055024</v>
+      </c>
+      <c r="D88" s="4">
+        <v>4000</v>
+      </c>
+      <c r="E88" s="4">
+        <v>3000000</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="89" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C89" s="7">
+        <v>69055031</v>
+      </c>
+      <c r="D89" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E89" s="4">
+        <v>3000000</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I89" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="90" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C90" s="7">
+        <v>69055032</v>
+      </c>
+      <c r="D90" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E90" s="4">
+        <v>3000000</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="91" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C91" s="7">
+        <v>69055033</v>
+      </c>
+      <c r="D91" s="4">
+        <v>4000</v>
+      </c>
+      <c r="E91" s="4">
+        <v>3000000</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="92" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C92" s="7">
+        <v>69055034</v>
+      </c>
+      <c r="D92" s="4">
+        <v>4000</v>
+      </c>
+      <c r="E92" s="4">
+        <v>3000000</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="93" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C93" s="7">
+        <v>60031231</v>
+      </c>
+      <c r="D93" s="4">
+        <v>5000</v>
+      </c>
+      <c r="E93" s="4">
+        <v>5000000</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I93" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="94" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C94" s="7">
+        <v>60031241</v>
+      </c>
+      <c r="D94" s="4">
+        <v>5000</v>
+      </c>
+      <c r="E94" s="4">
+        <v>5000000</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="95" spans="3:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C95" s="7">
+        <v>60031251</v>
+      </c>
+      <c r="D95" s="4">
+        <v>5000</v>
+      </c>
+      <c r="E95" s="4">
+        <v>5000000</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
